--- a/result/Result.xlsx
+++ b/result/Result.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Sports\FUT_PYTHON\result\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D377FB20-76A4-4C59-B5C1-B89CC7DEB6E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F083909-EE83-466F-9461-B4A717E6E0DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1950" yWindow="1500" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Lay 0x1" sheetId="1" r:id="rId1"/>
@@ -38,15 +38,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
-    <t>SPAIN 1</t>
-  </si>
-  <si>
-    <t>Villarreal</t>
-  </si>
-  <si>
-    <t>Real Sociedad</t>
-  </si>
-  <si>
     <t>Data</t>
   </si>
   <si>
@@ -84,6 +75,15 @@
   </si>
   <si>
     <t>Comissão</t>
+  </si>
+  <si>
+    <t>SPAIN 2</t>
+  </si>
+  <si>
+    <t>Wycombe</t>
+  </si>
+  <si>
+    <t>Port Vale</t>
   </si>
 </sst>
 </file>
@@ -144,7 +144,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -177,6 +177,8 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="21" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Moeda" xfId="1" builtinId="4"/>
@@ -458,13 +460,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:M3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="8.140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="7.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.140625" bestFit="1" customWidth="1"/>
     <col min="6" max="7" width="12" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="15.85546875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="13.28515625" bestFit="1" customWidth="1"/>
@@ -476,65 +479,61 @@
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="H1" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="K1" s="11" t="s">
         <v>8</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="I1" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="J1" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="K1" s="11" t="s">
-        <v>11</v>
       </c>
       <c r="L1" s="11"/>
       <c r="M1" s="4" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
-        <v>46101</v>
+        <v>46109</v>
       </c>
       <c r="B2" s="2">
-        <v>0.70833333333333337</v>
+        <v>0.5</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="F2" s="5">
-        <v>1.99</v>
-      </c>
-      <c r="G2" s="5">
-        <v>4</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="F2" s="5"/>
+      <c r="G2" s="5"/>
       <c r="H2" s="5">
         <v>16.5</v>
       </c>
@@ -546,7 +545,7 @@
         <v>14.5</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="L2" s="8">
         <v>1</v>
@@ -555,6 +554,13 @@
         <f>L2-(L2*0.065)</f>
         <v>0.93500000000000005</v>
       </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A3" s="13"/>
+      <c r="B3" s="12"/>
+      <c r="H3" s="6"/>
+      <c r="I3" s="6"/>
+      <c r="J3" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="1">
